--- a/구현_전_상세설계/05_데이터_구조_설정값_정의_초안.xlsx
+++ b/구현_전_상세설계/05_데이터_구조_설정값_정의_초안.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="1" r:id="R76ee513ff97e40e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구조 목록" sheetId="2" r:id="Rd6b31ddb3d0f4dfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터 필드 정의" sheetId="3" r:id="R48ad16b3eaff46bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enum 정의" sheetId="4" r:id="R4bc326ec52584019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQLite 스키마" sheetId="5" r:id="R6e5c6860eaaa417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값 목록" sheetId="6" r:id="R97a1c6dd35244154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODO 분류" sheetId="7" r:id="R1392994a72f64a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토 질문" sheetId="8" r:id="R0121acbd084e4650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="1" r:id="R9bbda660c08b4ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구조 목록" sheetId="2" r:id="R2befb7aa0fae419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터 필드 정의" sheetId="3" r:id="Rab677992f0d647d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enum 정의" sheetId="4" r:id="Re24ad2a318a949d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQLite 스키마" sheetId="5" r:id="Rbc94089d34364f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값 목록" sheetId="6" r:id="R89ab62020c3642da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODO 분류" sheetId="7" r:id="R2e2595e1d90d4274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토 질문" sheetId="8" r:id="Re080af34bdc24966"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6059,7 +6059,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra637949fdcc34957"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98026e8978d0426f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7074,7 +7074,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a84f8b988b5498c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f3c838c63604afb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14708,7 +14708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R225910571dbc4616"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9afbabe17fbe4990"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16785,6 +16785,30 @@
         <x:v>RecoveryPolicy 값과 혼용 금지</x:v>
       </x:c>
     </x:row>
+    <x:row r="88" ht="14" hidden="0" customHeight="1">
+      <x:c r="A88" t="str">
+        <x:v>NodeHealthState</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>STARTING / READY / DEGRADED / RECOVERING / INIT_BLOCKED / FAULT</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>노드 자체의 기동·준비·저하·복구·초기화 차단·고장 상태</x:v>
+      </x:c>
+      <x:c r="E88" t="str">
+        <x:v>Heartbeat / GetNodeStatus / InitializeNode</x:v>
+      </x:c>
+      <x:c r="F88" t="str">
+        <x:v>확정</x:v>
+      </x:c>
+      <x:c r="G88" t="str">
+        <x:v>RecoveryPolicy.START_BLOCKED와 혼용 금지</x:v>
+      </x:c>
+      <x:c r="H88" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -16803,7 +16827,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d6e77d559c14641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc59d2b48fb7347db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19253,7 +19277,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5782436e15bf4a03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb71216c1f8f34ba8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24190,7 +24214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c51b8461db24ca8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fee39f2d0084cd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25069,7 +25093,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f78e799eeeb4d1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R804eb48d171a4b9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25412,7 +25436,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eae1209309a4c77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f052024fa434b30"/>
   </x:tableParts>
 </x:worksheet>
 </file>